--- a/Data/Nombre_Edad_Ciudad.xlsx
+++ b/Data/Nombre_Edad_Ciudad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soniaestevez/Documents/GitHub/Programming-in-Data-Science/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96622B7-32ED-B242-BF02-858F939FADDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84154D6B-F4E6-5E4A-88DB-E8659B82BE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6680" yWindow="3640" windowWidth="28040" windowHeight="17440" xr2:uid="{5AA0E04C-731B-4244-9AE4-1188765F17DE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Nombre</t>
   </si>
@@ -53,13 +53,19 @@
   </si>
   <si>
     <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Nieves</t>
+  </si>
+  <si>
+    <t>Carlitos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -192,6 +198,12 @@
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -536,8 +548,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -933,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{712DD439-A21D-3B47-972D-B92B3DA03700}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -994,6 +1007,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
